--- a/template_pst.xlsx
+++ b/template_pst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Project_Web\Website_E-Perjadin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C809A6F9-CB9B-4E35-ADC2-14C1DB5B745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF10F27D-C29D-4A9C-8181-DEE040F3E472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{90350066-7765-4977-A66B-164B7EBDC2B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{90350066-7765-4977-A66B-164B7EBDC2B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Surat Tugas" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="108">
   <si>
     <t>DAFTAR  NOMINATIF</t>
   </si>
@@ -108,24 +108,6 @@
   </si>
   <si>
     <t>Penanggung  Jawab Kegiatan/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEMENTERIAN PERTANIAN </t>
-  </si>
-  <si>
-    <t>BADAN PERAKITAN DAN MODERNISASI PERTANIAN</t>
-  </si>
-  <si>
-    <t>PUSAT PERAKITAN DAN MODERNISASI PERTANIAN PERKEBUNAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JALAN TENTARA PELAJAR NOMOR 1 BOGOR 16111 </t>
-  </si>
-  <si>
-    <t>TELEPON (0251) 8384105</t>
-  </si>
-  <si>
-    <t>WEBSITE: perkebunan.brmp.pertanian.go.id E-MAIL: brmp.perkebunan@pertanian.go.id</t>
   </si>
   <si>
     <t>Mohon dengan hormat untuk mendapat  SURAT  PERJALANAN DINAS  (SPD) atas nama sbb :</t>
@@ -233,9 +215,6 @@
     <t>PUMK Perjalanan</t>
   </si>
   <si>
-    <t xml:space="preserve">                  </t>
-  </si>
-  <si>
     <t>SURAT TUGAS</t>
   </si>
   <si>
@@ -333,20 +312,6 @@
   </si>
   <si>
     <t>Penanggung Jawab Kegiatan</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="18"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">KEMENTERIAN PERTANIAN </t>
-    </r>
   </si>
   <si>
     <t>Pengadministrasi Perkantoran</t>
@@ -406,7 +371,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1387,10 +1352,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1419,10 +1384,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1442,7 +1406,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1452,13 +1416,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1479,7 +1443,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1489,18 +1453,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1509,13 +1468,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1529,22 +1488,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1561,8 +1518,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1572,7 +1529,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1584,7 +1541,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1599,7 +1556,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,7 +1584,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1661,13 +1617,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1695,10 +1649,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1708,8 +1662,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1724,13 +1678,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1744,6 +1695,81 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1780,34 +1806,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1831,97 +1866,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1945,128 +1896,57 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
+      <xdr:colOff>259963</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="140452" name="Line 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F55A0AD-54FE-DAA9-5E1F-D572AB6F3330}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="25400" y="1435100"/>
-          <a:ext cx="8750300" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="41275" cmpd="thickThin">
-          <a:solidFill>
-            <a:srgbClr val="00008A"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="140453" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182A15FE-5C2D-9F9D-FCFB-27A52776E36C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CD36164-A2A9-41B1-B303-B2E2210413E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect l="30870" t="19362" r="30664" b="69631"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="63500" y="57150"/>
-          <a:ext cx="1003300" cy="965200"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8866481" cy="1440089"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -2078,128 +1958,57 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:colOff>24262</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1450" name="Line 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EF9E6D0-4553-9D28-0CA2-868F3303DB1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="1377950"/>
-          <a:ext cx="7981950" cy="19050"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="41275" cmpd="thickThin">
-          <a:solidFill>
-            <a:srgbClr val="00008A"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>253863</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1451" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA14F644-8195-2C94-E1B0-EDD24CC01CFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FABC2E7-2D1A-4959-7A18-FE58AB4FC60E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect l="30870" t="19362" r="30664" b="69631"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="88900" y="120650"/>
-          <a:ext cx="977900" cy="927100"/>
+          <a:off x="24262" y="0"/>
+          <a:ext cx="8103601" cy="1316182"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -2470,7 +2279,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2485,112 +2294,98 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="158" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="158" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
-      <c r="C3" s="159" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
-      <c r="C4" s="160" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
-      <c r="C5" s="161" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="161"/>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
-      <c r="C6" s="162" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="162"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="F7" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="F7" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="157" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="157"/>
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="157"/>
+      <c r="A9" s="154" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="154"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="145" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
+      <c r="A10" s="160" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="40"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="145" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="145"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
+      <c r="A11" s="160" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="160"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="40"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -2604,88 +2399,88 @@
     </row>
     <row r="13" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="136" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="117" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="37"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="127" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="108" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="136" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="37"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="127" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="36"/>
     </row>
     <row r="15" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="136" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="117" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="37"/>
+      <c r="E15" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="36"/>
     </row>
     <row r="16" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="136" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="10"/>
+      <c r="C16" s="127" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="136" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="147"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="10"/>
+      <c r="C17" s="127" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="162"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2693,21 +2488,21 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2717,111 +2512,107 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="148" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="149"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23">
+    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="16"/>
+      <c r="B21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="163" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="164"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22">
         <v>1</v>
       </c>
-      <c r="C22" s="24" t="str">
+      <c r="C22" s="23" t="str">
         <f>'Permohonan Perjadin'!C15</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si.</v>
       </c>
-      <c r="D22" s="151" t="str">
+      <c r="D22" s="166" t="str">
         <f>'Permohonan Perjadin'!I15</f>
         <v>IV/d</v>
       </c>
-      <c r="E22" s="152"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="141" t="str">
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="131" t="str">
         <f>'Permohonan Perjadin'!F15</f>
         <v>Kepala Pusat</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="22"/>
-      <c r="B23" s="26">
+      <c r="H22" s="24"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="21"/>
+      <c r="B23" s="25">
         <v>2</v>
       </c>
-      <c r="C23" s="24" t="str">
+      <c r="C23" s="23" t="str">
         <f>'Permohonan Perjadin'!C16</f>
         <v>Hamdan Mubarok</v>
       </c>
-      <c r="D23" s="154" t="str">
+      <c r="D23" s="169" t="str">
         <f>'Permohonan Perjadin'!I16</f>
         <v>V</v>
       </c>
-      <c r="E23" s="155"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="142" t="str">
+      <c r="E23" s="170"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="132" t="str">
         <f>'Permohonan Perjadin'!F16</f>
         <v>Pengadministrasi Perkantoran</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="22"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="142"/>
-      <c r="H24" s="25"/>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="22"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="155"/>
-      <c r="F25" s="156"/>
-      <c r="G25" s="142"/>
-      <c r="H25" s="25"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="22"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="25"/>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="22"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="36"/>
-    </row>
-    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="21"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="169"/>
+      <c r="E24" s="170"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="24"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="21"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="170"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="24"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="21"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="24"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="21"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2831,150 +2622,150 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
     </row>
-    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
-      <c r="B29" s="136" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
+      <c r="B29" s="127" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="136" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="136" t="str">
+    <row r="30" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="36"/>
+      <c r="B30" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="127" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="127" t="str">
         <f>'Permohonan Perjadin'!E23</f>
         <v>Menghadiri Undangan Acara Munas Dekopi dan International Coffe Day 2026</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="136"/>
-      <c r="H30" s="39"/>
-    </row>
-    <row r="31" spans="1:10" ht="17.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="136">
+      <c r="F30" s="13"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="38"/>
+    </row>
+    <row r="31" spans="1:8" ht="17.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127">
         <f>'Permohonan Perjadin'!E24</f>
         <v>0</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="39"/>
-    </row>
-    <row r="32" spans="1:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="136" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="14" t="str">
+      <c r="F31" s="13"/>
+      <c r="G31" s="127"/>
+      <c r="H31" s="38"/>
+    </row>
+    <row r="32" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10"/>
+      <c r="B32" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="127" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="13" t="str">
         <f>'Permohonan Perjadin'!E26:F26</f>
         <v xml:space="preserve">30 September 2026 </v>
       </c>
-      <c r="F32" s="117" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="14" t="str">
+      <c r="F32" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="13" t="str">
         <f>'Permohonan Perjadin'!H26</f>
         <v>1 Oktober 2026</v>
       </c>
-      <c r="H32" s="39"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="136" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="136"/>
-      <c r="E33" s="136"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="39"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="127" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="38"/>
     </row>
     <row r="34" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="136" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136" t="str">
+      <c r="A34" s="10"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="127" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127" t="str">
         <f>Lampiran!I5</f>
         <v>( 7912.AEA.001.051.A.524111 )</v>
       </c>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="39"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="38"/>
     </row>
     <row r="35" spans="1:8" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" s="136" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="136"/>
-      <c r="E35" s="136"/>
-      <c r="F35" s="136"/>
-      <c r="G35" s="136"/>
-      <c r="H35" s="39"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="38"/>
     </row>
     <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="136"/>
-      <c r="C36" s="136" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="136"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="39"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="127"/>
+      <c r="C36" s="127" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="38"/>
     </row>
     <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="39"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="127"/>
+      <c r="C37" s="127"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="38"/>
     </row>
     <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="136"/>
-      <c r="C38" s="136" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="39"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="127"/>
+      <c r="C38" s="127" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="38"/>
     </row>
     <row r="39" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11"/>
@@ -2993,7 +2784,7 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="14" t="str">
+      <c r="G40" s="13" t="str">
         <f>'Permohonan Perjadin'!H29</f>
         <v>Bogor, 30 September 2026</v>
       </c>
@@ -3005,7 +2796,7 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="14"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="11"/>
@@ -3014,8 +2805,8 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="14" t="s">
-        <v>87</v>
+      <c r="G42" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -3025,8 +2816,8 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="14" t="s">
-        <v>88</v>
+      <c r="G43" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3036,7 +2827,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="13"/>
+      <c r="G44" s="10"/>
       <c r="H44" s="11"/>
     </row>
     <row r="45" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3046,7 +2837,7 @@
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="13"/>
+      <c r="G45" s="10"/>
       <c r="H45" s="11"/>
     </row>
     <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -3056,8 +2847,8 @@
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="13" t="s">
-        <v>84</v>
+      <c r="G46" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -3067,12 +2858,20 @@
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="13" t="s">
-        <v>89</v>
+      <c r="G47" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -3080,14 +2879,6 @@
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D23:F23"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
@@ -3107,7 +2898,7 @@
     <col min="5" max="5" width="9.453125" customWidth="1"/>
     <col min="6" max="6" width="6.1796875" customWidth="1"/>
     <col min="7" max="7" width="6.453125" customWidth="1"/>
-    <col min="8" max="8" width="25.81640625" style="41" customWidth="1"/>
+    <col min="8" max="8" width="25.81640625" style="40" customWidth="1"/>
     <col min="9" max="9" width="28.54296875" customWidth="1"/>
     <col min="10" max="10" width="3.6328125" customWidth="1"/>
     <col min="11" max="11" width="14.6328125" hidden="1" customWidth="1"/>
@@ -3115,597 +2906,573 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H1" s="42"/>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C2" s="182" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
     </row>
     <row r="3" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="158" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="68"/>
-      <c r="L3" s="68"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="62"/>
+      <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="C4" s="183" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="183"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
-      <c r="I4" s="183"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="180"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
       <c r="J4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C5" s="184" t="s">
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+    </row>
+    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="172"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="63"/>
+      <c r="L7" s="63"/>
+    </row>
+    <row r="8" spans="1:12" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:12" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="42"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="43"/>
+      <c r="B13" s="189" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="173" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="174"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="173" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-    </row>
-    <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="185" t="s">
+      <c r="G13" s="174"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="185"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-    </row>
-    <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="179" t="s">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="43"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="177"/>
+      <c r="H14" s="178"/>
+      <c r="I14" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="179"/>
-      <c r="E7" s="179"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="179"/>
-      <c r="H7" s="179"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="69"/>
-      <c r="L7" s="69"/>
-    </row>
-    <row r="8" spans="1:12" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="H8" s="42"/>
-    </row>
-    <row r="9" spans="1:12" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="H9" s="42"/>
-    </row>
-    <row r="10" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="43"/>
-      <c r="B10" s="27" t="s">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="46"/>
+      <c r="B15" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="191" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="192"/>
+      <c r="H15" s="193"/>
+      <c r="I15" s="66" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="46"/>
+      <c r="B16" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="192"/>
+      <c r="H16" s="193"/>
+      <c r="I16" s="66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="46"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="192"/>
+      <c r="H17" s="193"/>
+      <c r="I17" s="66"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="46"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="191"/>
+      <c r="G18" s="192"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="66"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="46"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="67"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="46"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="123" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="12"/>
+      <c r="B22" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="129" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="129" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12"/>
+      <c r="B23" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="129" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="48"/>
+    </row>
+    <row r="24" spans="1:9" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="12"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="48"/>
+    </row>
+    <row r="25" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12"/>
+      <c r="B25" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="129" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="129" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="130"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="26"/>
+    </row>
+    <row r="26" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12"/>
+      <c r="B26" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="129" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="43"/>
-    </row>
-    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="46"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="47"/>
-      <c r="B13" s="171" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="180" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="177"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="180" t="s">
+      <c r="F26" s="192"/>
+      <c r="G26" s="118" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="118" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="12"/>
+      <c r="B27" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="177"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="70" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="47"/>
-      <c r="B14" s="172"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="165"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="71" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="50"/>
-      <c r="B15" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="173" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="174"/>
-      <c r="H15" s="175"/>
-      <c r="I15" s="72" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="173" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="174"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="72" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="50"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="175"/>
-      <c r="I17" s="72"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="50"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="174"/>
-      <c r="H18" s="175"/>
-      <c r="I18" s="72"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="50"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="73"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="50"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-    </row>
-    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="132" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-    </row>
-    <row r="22" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="43"/>
-      <c r="B22" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="139" t="s">
+      <c r="E27" s="194" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="192"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="27"/>
-    </row>
-    <row r="23" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="43"/>
-      <c r="B23" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="27"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="52"/>
-    </row>
-    <row r="24" spans="1:9" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="43"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="52"/>
-    </row>
-    <row r="25" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="43"/>
-      <c r="B25" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="139" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="43"/>
-      <c r="B26" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="176" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="174"/>
-      <c r="G26" s="127" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="127" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="43"/>
-      <c r="B27" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="176" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="174"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="43"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
-      <c r="B30" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43" t="s">
-        <v>49</v>
+      <c r="B30" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="62" t="s">
-        <v>97</v>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="57" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="62"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="57"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="62"/>
-      <c r="J33" s="61"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="57"/>
+      <c r="J33" s="56"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="62"/>
-      <c r="J34" s="62"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="57"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
-      <c r="B35" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="126" t="s">
-        <v>84</v>
-      </c>
-      <c r="J35" s="61"/>
+      <c r="B35" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="117" t="s">
+        <v>77</v>
+      </c>
+      <c r="J35" s="56"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
-      <c r="B36" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="62"/>
+      <c r="B36" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="57"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="J37" s="62"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="J37" s="57"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="122" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="E41" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="43"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="E43" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="43"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="43"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-    </row>
-    <row r="40" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="43"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="E41" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-    </row>
-    <row r="42" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="47"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="43"/>
-      <c r="E43" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-    </row>
-    <row r="44" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="47"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-    </row>
-    <row r="46" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="47"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-    </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12"/>
@@ -3715,9 +3482,9 @@
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
       <c r="G48" s="12"/>
-      <c r="H48" s="43"/>
-    </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -3725,69 +3492,69 @@
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
       <c r="G49" s="12"/>
-      <c r="H49" s="43"/>
-    </row>
-    <row r="50" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
-      <c r="B50" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="164"/>
-      <c r="D50" s="167" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" s="168"/>
-      <c r="F50" s="44"/>
+      <c r="B50" s="183" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="184"/>
+      <c r="D50" s="185" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="186"/>
+      <c r="F50" s="41"/>
       <c r="G50" s="12"/>
-      <c r="H50" s="43"/>
-    </row>
-    <row r="51" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
-      <c r="B51" s="165"/>
-      <c r="C51" s="166"/>
-      <c r="D51" s="169"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="44"/>
+      <c r="B51" s="176"/>
+      <c r="C51" s="178"/>
+      <c r="D51" s="187"/>
+      <c r="E51" s="188"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="12"/>
-      <c r="H51" s="43"/>
-    </row>
-    <row r="52" spans="1:9" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="1:8" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
-      <c r="B52" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="43"/>
+      <c r="B52" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="59"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="12"/>
       <c r="G52" s="12"/>
-      <c r="H52" s="43"/>
-    </row>
-    <row r="53" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
-      <c r="B53" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" s="64"/>
-      <c r="D53" s="65"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="43"/>
+      <c r="B53" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="59"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="12"/>
       <c r="G53" s="12"/>
-      <c r="H53" s="43"/>
-    </row>
-    <row r="54" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
-      <c r="B54" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" s="64"/>
-      <c r="D54" s="65"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="43"/>
+      <c r="B54" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="59"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="12"/>
       <c r="G54" s="12"/>
-      <c r="H54" s="43"/>
-    </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3795,213 +3562,158 @@
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
-      <c r="H55" s="43"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="42"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-    </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H65" s="42"/>
-      <c r="I65" s="42"/>
-    </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-    </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H67" s="42"/>
-      <c r="I67" s="42"/>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-    </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
-    </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-    </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-    </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
-    </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
-    </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H74" s="42"/>
-      <c r="I74" s="42"/>
-    </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H75" s="42"/>
-      <c r="I75" s="42"/>
-    </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H76" s="42"/>
-      <c r="I76" s="42"/>
-    </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H77" s="42"/>
-      <c r="I77" s="42"/>
-    </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H78" s="42"/>
-      <c r="I78" s="42"/>
-    </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-    </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H80" s="42"/>
-      <c r="I80" s="42"/>
-    </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H81" s="42"/>
-      <c r="I81" s="42"/>
-    </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H82" s="42"/>
-      <c r="I82" s="42"/>
-    </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H83" s="42"/>
-      <c r="I83" s="42"/>
-    </row>
-    <row r="84" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H84" s="42"/>
-      <c r="I84" s="42"/>
-    </row>
-    <row r="85" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H85" s="42"/>
-      <c r="I85" s="42"/>
-    </row>
-    <row r="86" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H86" s="42"/>
-      <c r="I86" s="42"/>
-    </row>
-    <row r="87" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H87" s="42"/>
-      <c r="I87" s="42"/>
-    </row>
-    <row r="88" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H88" s="42"/>
-      <c r="I88" s="42"/>
-    </row>
-    <row r="89" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H89" s="42"/>
-      <c r="I89" s="42"/>
-    </row>
-    <row r="90" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H90" s="42"/>
-      <c r="I90" s="42"/>
-    </row>
-    <row r="91" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H91" s="42"/>
-      <c r="I91" s="42"/>
-    </row>
-    <row r="92" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H92" s="42"/>
-      <c r="I92" s="42"/>
-    </row>
-    <row r="93" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H93" s="42"/>
-      <c r="I93" s="42"/>
-    </row>
-    <row r="94" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H94" s="42"/>
-      <c r="I94" s="42"/>
-    </row>
-    <row r="95" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H95" s="42"/>
-      <c r="I95" s="42"/>
-    </row>
-    <row r="96" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H96" s="42"/>
-      <c r="I96" s="42"/>
-    </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H97" s="42"/>
-      <c r="I97" s="42"/>
-    </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H98" s="42"/>
-      <c r="I98" s="42"/>
-    </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H99" s="42"/>
-      <c r="I99" s="42"/>
-    </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H100" s="42"/>
-      <c r="I100" s="42"/>
-    </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H101" s="42"/>
-      <c r="I101" s="42"/>
-    </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.35">
-      <c r="H102" s="42"/>
-      <c r="I102" s="42"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="39"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H87"/>
+    </row>
+    <row r="88" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H88"/>
+    </row>
+    <row r="89" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H89"/>
+    </row>
+    <row r="90" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H90"/>
+    </row>
+    <row r="91" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H91"/>
+    </row>
+    <row r="92" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H92"/>
+    </row>
+    <row r="93" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H93"/>
+    </row>
+    <row r="94" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H94"/>
+    </row>
+    <row r="95" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H95"/>
+    </row>
+    <row r="96" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H96"/>
+    </row>
+    <row r="97" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H97"/>
+    </row>
+    <row r="98" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H98"/>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H99"/>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H100"/>
+    </row>
+    <row r="101" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H101"/>
+    </row>
+    <row r="102" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H102"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="B50:C51"/>
     <mergeCell ref="D50:E51"/>
     <mergeCell ref="B13:B14"/>
@@ -4012,6 +3724,14 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
@@ -4045,619 +3765,609 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="199" t="s">
+      <c r="A2" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="199"/>
-      <c r="K2" s="199"/>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
-      <c r="N2" s="199"/>
-      <c r="O2" s="199"/>
-      <c r="P2" s="199"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="135"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="199" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="199"/>
-      <c r="N3" s="199"/>
-      <c r="O3" s="199"/>
-      <c r="P3" s="199"/>
+      <c r="A3" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="200"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="200"/>
-      <c r="H4" s="200"/>
-      <c r="I4" s="200"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="200"/>
-      <c r="L4" s="200"/>
-      <c r="M4" s="200"/>
-      <c r="N4" s="200"/>
-      <c r="O4" s="200"/>
-      <c r="P4" s="200"/>
+      <c r="A4" s="136"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="136"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
     </row>
     <row r="5" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="40"/>
-      <c r="B5" s="74" t="s">
+      <c r="A5" s="39"/>
+      <c r="B5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="75" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="128" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="128"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
+      <c r="C5" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="119"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
     </row>
     <row r="6" spans="1:17" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
     </row>
     <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="189" t="s">
+      <c r="B7" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="189" t="s">
+      <c r="D7" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="201" t="s">
+      <c r="G7" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="201"/>
-      <c r="I7" s="191" t="s">
+      <c r="H7" s="137"/>
+      <c r="I7" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="191" t="s">
+      <c r="J7" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="122" t="s">
+      <c r="K7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="194" t="s">
+      <c r="L7" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="194" t="s">
+      <c r="M7" s="149" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="76"/>
-      <c r="O7" s="124" t="s">
+      <c r="N7" s="70"/>
+      <c r="O7" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="197" t="s">
+      <c r="P7" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="112"/>
     </row>
     <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="188"/>
-      <c r="B8" s="190"/>
-      <c r="C8" s="77" t="s">
+      <c r="A8" s="143"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="190"/>
-      <c r="E8" s="77" t="s">
+      <c r="D8" s="145"/>
+      <c r="E8" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="202" t="s">
+      <c r="G8" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="203"/>
-      <c r="I8" s="192"/>
-      <c r="J8" s="193"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="195"/>
-      <c r="M8" s="196"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="125" t="s">
+      <c r="H8" s="139"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="151"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="112"/>
+      <c r="P8" s="153"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="78">
+      <c r="A9" s="72">
         <v>1</v>
       </c>
-      <c r="B9" s="79" t="str">
+      <c r="B9" s="73" t="str">
         <f>'Permohonan Perjadin'!C15</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si.</v>
       </c>
-      <c r="C9" s="129" t="s">
+      <c r="C9" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="135" t="str">
+      <c r="D9" s="126" t="str">
         <f>'Permohonan Perjadin'!E22</f>
         <v>Jakarta</v>
       </c>
-      <c r="E9" s="80" t="str">
+      <c r="E9" s="74" t="str">
         <f>'Permohonan Perjadin'!E26</f>
         <v xml:space="preserve">30 September 2026 </v>
       </c>
-      <c r="F9" s="80" t="str">
+      <c r="F9" s="74" t="str">
         <f>'Permohonan Perjadin'!H26</f>
         <v>1 Oktober 2026</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="75">
         <v>2</v>
       </c>
-      <c r="H9" s="121" t="s">
+      <c r="H9" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>530000</v>
       </c>
-      <c r="J9" s="120">
+      <c r="J9" s="111">
         <f>G9*I9</f>
         <v>1060000</v>
       </c>
-      <c r="K9" s="100"/>
-      <c r="L9" s="101"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="100"/>
-      <c r="O9" s="100">
+      <c r="K9" s="93"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="93"/>
+      <c r="O9" s="93">
         <f>150000*2</f>
         <v>300000</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="95">
         <f>SUM(J9:O9)</f>
         <v>1360000</v>
       </c>
-      <c r="Q9" s="113"/>
+      <c r="Q9" s="92"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="82">
+      <c r="A10" s="76">
         <v>2</v>
       </c>
-      <c r="B10" s="83" t="str">
+      <c r="B10" s="77" t="str">
         <f>'Permohonan Perjadin'!C16</f>
         <v>Hamdan Mubarok</v>
       </c>
-      <c r="C10" s="130" t="s">
+      <c r="C10" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="84" t="str">
+      <c r="D10" s="78" t="str">
         <f>'Permohonan Perjadin'!E22</f>
         <v>Jakarta</v>
       </c>
-      <c r="E10" s="134" t="str">
+      <c r="E10" s="125" t="str">
         <f>'Permohonan Perjadin'!E26</f>
         <v xml:space="preserve">30 September 2026 </v>
       </c>
-      <c r="F10" s="85" t="str">
+      <c r="F10" s="79" t="str">
         <f>F9</f>
         <v>1 Oktober 2026</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="80">
         <v>2</v>
       </c>
-      <c r="H10" s="118" t="str">
+      <c r="H10" s="109" t="str">
         <f>H9</f>
         <v>Hari</v>
       </c>
-      <c r="I10" s="101">
+      <c r="I10" s="94">
         <v>200000</v>
       </c>
-      <c r="J10" s="119">
+      <c r="J10" s="110">
         <f>G10*I10</f>
         <v>400000</v>
       </c>
-      <c r="K10" s="101"/>
-      <c r="L10" s="143">
+      <c r="K10" s="94"/>
+      <c r="L10" s="133">
         <f>565000+565000</f>
         <v>1130000</v>
       </c>
-      <c r="M10" s="101"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="103">
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="96">
         <f>SUM(J10:O10)</f>
         <v>1530000</v>
       </c>
-      <c r="Q10" s="113"/>
+      <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="134"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="101"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="101"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="113"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="92"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="113"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="94"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="112"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="98"/>
     </row>
     <row r="14" spans="1:17" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94" t="s">
+      <c r="A14" s="87"/>
+      <c r="B14" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="107">
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="100">
         <f>SUM(J9:J13)</f>
         <v>1460000</v>
       </c>
-      <c r="K14" s="107">
+      <c r="K14" s="100">
         <f>SUM(K9:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="107">
+      <c r="L14" s="100">
         <f>SUM(L9:L13)</f>
         <v>1130000</v>
       </c>
-      <c r="M14" s="107">
+      <c r="M14" s="100">
         <f>SUM(M9:M13)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="107"/>
-      <c r="O14" s="107">
+      <c r="N14" s="100"/>
+      <c r="O14" s="100">
         <f>SUM(O9:O13)</f>
         <v>300000</v>
       </c>
-      <c r="P14" s="108">
+      <c r="P14" s="101">
         <f>SUM(J14:O14)</f>
         <v>2890000</v>
       </c>
-      <c r="Q14" s="114"/>
+      <c r="Q14" s="105"/>
     </row>
     <row r="15" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="112"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40" t="s">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40" t="str">
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39" t="str">
         <f>'Permohonan Perjadin'!H29</f>
         <v>Bogor, 30 September 2026</v>
       </c>
-      <c r="O16" s="110"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="115"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="106"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="116"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="106"/>
+      <c r="R17" s="107"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="116"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="R18" s="107"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="113"/>
-      <c r="R19" s="116"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="107"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="116"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="107"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="R21" s="116"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="R21" s="107"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="R22" s="116"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="R22" s="107"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="40"/>
-      <c r="B23" s="98" t="str">
+      <c r="A23" s="39"/>
+      <c r="B23" s="68" t="str">
         <f>'Permohonan Perjadin'!B35</f>
         <v>Rifki Zainaldi, S.E., M.M</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="204" t="str">
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="140" t="str">
         <f>'Permohonan Perjadin'!H35</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si</v>
       </c>
-      <c r="O23" s="204"/>
-      <c r="P23" s="204"/>
-      <c r="R23" s="116"/>
+      <c r="O23" s="140"/>
+      <c r="P23" s="140"/>
+      <c r="R23" s="107"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40" t="str">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39" t="str">
         <f>'Permohonan Perjadin'!B36</f>
         <v>NIP. 197712072011011002</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="186" t="str">
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="141" t="str">
         <f>'Permohonan Perjadin'!H36</f>
         <v>NIP. 196904191998031002</v>
       </c>
-      <c r="O24" s="186"/>
-      <c r="P24" s="186"/>
-      <c r="R24" s="116"/>
+      <c r="O24" s="141"/>
+      <c r="P24" s="141"/>
+      <c r="R24" s="107"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D31" s="99"/>
+      <c r="D31" s="92"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D32" s="99"/>
+      <c r="D32" s="92"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D33" s="99"/>
+      <c r="D33" s="92"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D34" s="99"/>
+      <c r="D34" s="92"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D35" s="99"/>
+      <c r="D35" s="92"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D36" s="99"/>
+      <c r="D36" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="A7:A8"/>
@@ -4668,6 +4378,11 @@
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.55118110236220474" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/template_pst.xlsx
+++ b/template_pst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Project_Web\Website_E-Perjadin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF10F27D-C29D-4A9C-8181-DEE040F3E472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7A647-72FA-41F2-B1DE-1E79E559DFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{90350066-7765-4977-A66B-164B7EBDC2B4}"/>
   </bookViews>
@@ -1695,6 +1695,171 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1709,171 +1874,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1899,15 +1899,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>228985</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>259963</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>4130</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1922,28 +1922,25 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="30870" t="19362" r="30664" b="69631"/>
+        <a:srcRect/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8866481" cy="1440089"/>
+          <a:off x="228985" y="0"/>
+          <a:ext cx="8675447" cy="1432880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
         <a:extLst>
           <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
             <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -1961,22 +1958,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>24262</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>253863</xdr:colOff>
+      <xdr:colOff>234699</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:rowOff>92364</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FABC2E7-2D1A-4959-7A18-FE58AB4FC60E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{692EE0FA-F083-4412-903B-C1014FE1CC57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1984,28 +1981,25 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="30870" t="19362" r="30664" b="69631"/>
+        <a:srcRect/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="24262" y="0"/>
-          <a:ext cx="8103601" cy="1316182"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8108699" cy="1339273"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
         <a:extLst>
           <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
             <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -2294,96 +2288,96 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
-      <c r="C6" s="159"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
+      <c r="C6" s="152"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="152"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="152"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F7" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="154" t="s">
+      <c r="A9" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
+      <c r="B9" s="147"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="138"/>
       <c r="H10" s="10"/>
       <c r="I10" s="39"/>
     </row>
     <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="160" t="s">
+      <c r="A11" s="138" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="160"/>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="160"/>
-      <c r="F11" s="160"/>
-      <c r="G11" s="160"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
       <c r="H11" s="10"/>
       <c r="I11" s="39"/>
     </row>
@@ -2473,11 +2467,11 @@
       <c r="D17" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="161" t="s">
+      <c r="E17" s="139" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="162"/>
-      <c r="G17" s="162"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2520,11 +2514,11 @@
       <c r="C21" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="163" t="s">
+      <c r="D21" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="164"/>
-      <c r="F21" s="165"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="143"/>
       <c r="G21" s="19" t="s">
         <v>30</v>
       </c>
@@ -2539,12 +2533,12 @@
         <f>'Permohonan Perjadin'!C15</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si.</v>
       </c>
-      <c r="D22" s="166" t="str">
+      <c r="D22" s="144" t="str">
         <f>'Permohonan Perjadin'!I15</f>
         <v>IV/d</v>
       </c>
-      <c r="E22" s="167"/>
-      <c r="F22" s="168"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="146"/>
       <c r="G22" s="131" t="str">
         <f>'Permohonan Perjadin'!F15</f>
         <v>Kepala Pusat</v>
@@ -2560,12 +2554,12 @@
         <f>'Permohonan Perjadin'!C16</f>
         <v>Hamdan Mubarok</v>
       </c>
-      <c r="D23" s="169" t="str">
+      <c r="D23" s="135" t="str">
         <f>'Permohonan Perjadin'!I16</f>
         <v>V</v>
       </c>
-      <c r="E23" s="170"/>
-      <c r="F23" s="171"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="137"/>
       <c r="G23" s="132" t="str">
         <f>'Permohonan Perjadin'!F16</f>
         <v>Pengadministrasi Perkantoran</v>
@@ -2576,9 +2570,9 @@
       <c r="A24" s="21"/>
       <c r="B24" s="25"/>
       <c r="C24" s="23"/>
-      <c r="D24" s="169"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="171"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="137"/>
       <c r="G24" s="132"/>
       <c r="H24" s="24"/>
     </row>
@@ -2586,9 +2580,9 @@
       <c r="A25" s="21"/>
       <c r="B25" s="25"/>
       <c r="C25" s="23"/>
-      <c r="D25" s="169"/>
-      <c r="E25" s="170"/>
-      <c r="F25" s="171"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="137"/>
       <c r="G25" s="132"/>
       <c r="H25" s="24"/>
     </row>
@@ -2864,6 +2858,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D23:F23"/>
@@ -2872,13 +2873,6 @@
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
@@ -2909,62 +2903,62 @@
       <c r="H1"/>
     </row>
     <row r="2" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
       <c r="J3" s="62"/>
       <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="C4" s="180"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="180"/>
+      <c r="C4" s="173"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="173"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="174"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="182"/>
-      <c r="I6" s="182"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="175"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="175"/>
+      <c r="I6" s="175"/>
     </row>
     <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="172"/>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="172"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
       <c r="J7" s="63"/>
       <c r="L7" s="63"/>
     </row>
@@ -3008,32 +3002,32 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="43"/>
-      <c r="B13" s="189" t="s">
+      <c r="B13" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="173" t="s">
+      <c r="C13" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="174"/>
+      <c r="D13" s="167"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="173" t="s">
+      <c r="F13" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="174"/>
-      <c r="H13" s="175"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="171"/>
       <c r="I13" s="64" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="43"/>
-      <c r="B14" s="190"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="177"/>
+      <c r="B14" s="162"/>
+      <c r="C14" s="155"/>
+      <c r="D14" s="168"/>
       <c r="E14" s="45"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="178"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="168"/>
+      <c r="H14" s="156"/>
       <c r="I14" s="65" t="s">
         <v>32</v>
       </c>
@@ -3048,11 +3042,11 @@
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="191" t="s">
+      <c r="F15" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="192"/>
-      <c r="H15" s="193"/>
+      <c r="G15" s="164"/>
+      <c r="H15" s="165"/>
       <c r="I15" s="66" t="s">
         <v>88</v>
       </c>
@@ -3067,11 +3061,11 @@
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
-      <c r="F16" s="191" t="s">
+      <c r="F16" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="192"/>
-      <c r="H16" s="193"/>
+      <c r="G16" s="164"/>
+      <c r="H16" s="165"/>
       <c r="I16" s="66" t="s">
         <v>83</v>
       </c>
@@ -3082,9 +3076,9 @@
       <c r="C17" s="15"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
-      <c r="F17" s="191"/>
-      <c r="G17" s="192"/>
-      <c r="H17" s="193"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="164"/>
+      <c r="H17" s="165"/>
       <c r="I17" s="66"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -3093,9 +3087,9 @@
       <c r="C18" s="15"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
-      <c r="F18" s="191"/>
-      <c r="G18" s="192"/>
-      <c r="H18" s="193"/>
+      <c r="F18" s="163"/>
+      <c r="G18" s="164"/>
+      <c r="H18" s="165"/>
       <c r="I18" s="66"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -3197,10 +3191,10 @@
       <c r="D26" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="194" t="s">
+      <c r="E26" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="192"/>
+      <c r="F26" s="164"/>
       <c r="G26" s="118" t="s">
         <v>98</v>
       </c>
@@ -3217,10 +3211,10 @@
       <c r="D27" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="194" t="s">
+      <c r="E27" s="166" t="s">
         <v>84</v>
       </c>
-      <c r="F27" s="192"/>
+      <c r="F27" s="164"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
     </row>
@@ -3496,24 +3490,24 @@
     </row>
     <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
-      <c r="B50" s="183" t="s">
+      <c r="B50" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="184"/>
-      <c r="D50" s="185" t="s">
+      <c r="C50" s="154"/>
+      <c r="D50" s="157" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="186"/>
+      <c r="E50" s="158"/>
       <c r="F50" s="41"/>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
-      <c r="B51" s="176"/>
-      <c r="C51" s="178"/>
-      <c r="D51" s="187"/>
-      <c r="E51" s="188"/>
+      <c r="B51" s="155"/>
+      <c r="C51" s="156"/>
+      <c r="D51" s="159"/>
+      <c r="E51" s="160"/>
       <c r="F51" s="41"/>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
@@ -3714,6 +3708,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="B50:C51"/>
     <mergeCell ref="D50:E51"/>
     <mergeCell ref="B13:B14"/>
@@ -3724,14 +3726,6 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
@@ -3765,62 +3759,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="190" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="190"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="190"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="190"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="190" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="135"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
+      <c r="L3" s="190"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="136"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="136"/>
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
+      <c r="A4" s="191"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="191"/>
+      <c r="M4" s="191"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="191"/>
+      <c r="P4" s="191"/>
     </row>
     <row r="5" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39"/>
@@ -3864,16 +3858,16 @@
       <c r="P6" s="39"/>
     </row>
     <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="180" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="144" t="s">
+      <c r="D7" s="180" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="70" t="s">
@@ -3882,60 +3876,60 @@
       <c r="F7" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="137" t="s">
+      <c r="G7" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="137"/>
-      <c r="I7" s="146" t="s">
+      <c r="H7" s="192"/>
+      <c r="I7" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="146" t="s">
+      <c r="J7" s="182" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="149" t="s">
+      <c r="L7" s="185" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="149" t="s">
+      <c r="M7" s="185" t="s">
         <v>13</v>
       </c>
       <c r="N7" s="70"/>
       <c r="O7" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="152" t="s">
+      <c r="P7" s="188" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="143"/>
-      <c r="B8" s="145"/>
+      <c r="A8" s="179"/>
+      <c r="B8" s="181"/>
       <c r="C8" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="145"/>
+      <c r="D8" s="181"/>
       <c r="E8" s="71" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="138" t="s">
+      <c r="G8" s="193" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="139"/>
-      <c r="I8" s="147"/>
-      <c r="J8" s="148"/>
+      <c r="H8" s="194"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="184"/>
       <c r="K8" s="114"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="151"/>
+      <c r="L8" s="186"/>
+      <c r="M8" s="187"/>
       <c r="N8" s="71"/>
       <c r="O8" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="153"/>
+      <c r="P8" s="189"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A9" s="72">
@@ -4315,12 +4309,12 @@
       <c r="K23" s="39"/>
       <c r="L23" s="39"/>
       <c r="M23" s="39"/>
-      <c r="N23" s="140" t="str">
+      <c r="N23" s="176" t="str">
         <f>'Permohonan Perjadin'!H35</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si</v>
       </c>
-      <c r="O23" s="140"/>
-      <c r="P23" s="140"/>
+      <c r="O23" s="176"/>
+      <c r="P23" s="176"/>
       <c r="R23" s="107"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -4340,12 +4334,12 @@
       <c r="K24" s="39"/>
       <c r="L24" s="39"/>
       <c r="M24" s="39"/>
-      <c r="N24" s="141" t="str">
+      <c r="N24" s="177" t="str">
         <f>'Permohonan Perjadin'!H36</f>
         <v>NIP. 196904191998031002</v>
       </c>
-      <c r="O24" s="141"/>
-      <c r="P24" s="141"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="177"/>
       <c r="R24" s="107"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -4368,6 +4362,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="A7:A8"/>
@@ -4378,11 +4377,6 @@
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.55118110236220474" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/template_pst.xlsx
+++ b/template_pst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Project_Web\Website_E-Perjadin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7A647-72FA-41F2-B1DE-1E79E559DFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFECF645-E936-4D4D-9D3A-0F8BBF86A515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{90350066-7765-4977-A66B-164B7EBDC2B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{90350066-7765-4977-A66B-164B7EBDC2B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Surat Tugas" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="105">
   <si>
     <t>DAFTAR  NOMINATIF</t>
   </si>
@@ -290,15 +290,9 @@
     <t>NIP. 196904191998031002</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>Dinas</t>
   </si>
   <si>
-    <t>Hamdan Mubarok</t>
-  </si>
-  <si>
     <t>Dr. Ir. I Ketut Kariyasa, M.Si.</t>
   </si>
   <si>
@@ -314,9 +308,6 @@
     <t>Penanggung Jawab Kegiatan</t>
   </si>
   <si>
-    <t>Pengadministrasi Perkantoran</t>
-  </si>
-  <si>
     <t>Rp.  ...……………………</t>
   </si>
   <si>
@@ -326,9 +317,6 @@
     <t>( 7912.AEA.001.051.A.524111 )</t>
   </si>
   <si>
-    <t>TOLAK UKUR  ( 7912.AEA.001.051.A.524111 )</t>
-  </si>
-  <si>
     <t>Bersama ini kami penanggung jawab kegiatan   : Pendampingan Program Strategis Swasembada Pangan Berkelanjutan</t>
   </si>
   <si>
@@ -363,6 +351,9 @@
   </si>
   <si>
     <t>Bogor, 30 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOLAK UKUR  </t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1346,7 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1695,6 +1686,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1731,34 +1740,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1773,12 +1791,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1791,32 +1803,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1860,20 +1860,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2288,96 +2291,96 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F7" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="147"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="138" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="138"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
+      <c r="A10" s="144" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
       <c r="H10" s="10"/>
       <c r="I10" s="39"/>
     </row>
     <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="138" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
+      <c r="A11" s="144" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="144"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
       <c r="H11" s="10"/>
       <c r="I11" s="39"/>
     </row>
@@ -2467,11 +2470,11 @@
       <c r="D17" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="139" t="s">
+      <c r="E17" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="146"/>
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2514,11 +2517,11 @@
       <c r="C21" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="141" t="s">
+      <c r="D21" s="147" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="142"/>
-      <c r="F21" s="143"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="149"/>
       <c r="G21" s="19" t="s">
         <v>30</v>
       </c>
@@ -2533,12 +2536,12 @@
         <f>'Permohonan Perjadin'!C15</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si.</v>
       </c>
-      <c r="D22" s="144" t="str">
+      <c r="D22" s="150" t="str">
         <f>'Permohonan Perjadin'!I15</f>
         <v>IV/d</v>
       </c>
-      <c r="E22" s="145"/>
-      <c r="F22" s="146"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="152"/>
       <c r="G22" s="131" t="str">
         <f>'Permohonan Perjadin'!F15</f>
         <v>Kepala Pusat</v>
@@ -2547,32 +2550,21 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21"/>
-      <c r="B23" s="25">
-        <v>2</v>
-      </c>
-      <c r="C23" s="23" t="str">
-        <f>'Permohonan Perjadin'!C16</f>
-        <v>Hamdan Mubarok</v>
-      </c>
-      <c r="D23" s="135" t="str">
-        <f>'Permohonan Perjadin'!I16</f>
-        <v>V</v>
-      </c>
-      <c r="E23" s="136"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="132" t="str">
-        <f>'Permohonan Perjadin'!F16</f>
-        <v>Pengadministrasi Perkantoran</v>
-      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="132"/>
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21"/>
       <c r="B24" s="25"/>
       <c r="C24" s="23"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="143"/>
       <c r="G24" s="132"/>
       <c r="H24" s="24"/>
     </row>
@@ -2580,9 +2572,9 @@
       <c r="A25" s="21"/>
       <c r="B25" s="25"/>
       <c r="C25" s="23"/>
-      <c r="D25" s="135"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="137"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="143"/>
       <c r="G25" s="132"/>
       <c r="H25" s="24"/>
     </row>
@@ -2702,7 +2694,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="37"/>
       <c r="C34" s="127" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34" s="127"/>
       <c r="E34" s="127" t="str">
@@ -2858,13 +2850,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D23:F23"/>
@@ -2873,6 +2858,13 @@
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
@@ -2903,62 +2895,62 @@
       <c r="H1"/>
     </row>
     <row r="2" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
     </row>
     <row r="3" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
       <c r="J3" s="62"/>
       <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
       <c r="J4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="162"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="175"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="C6" s="163"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
     </row>
     <row r="7" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
       <c r="J7" s="63"/>
       <c r="L7" s="63"/>
     </row>
@@ -2971,7 +2963,7 @@
     <row r="10" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -3002,32 +2994,32 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="43"/>
-      <c r="B13" s="161" t="s">
+      <c r="B13" s="197" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="170" t="s">
+      <c r="C13" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="167"/>
+      <c r="D13" s="155"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="170" t="s">
+      <c r="F13" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="167"/>
-      <c r="H13" s="171"/>
+      <c r="G13" s="155"/>
+      <c r="H13" s="156"/>
       <c r="I13" s="64" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="43"/>
-      <c r="B14" s="162"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="168"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="158"/>
       <c r="E14" s="45"/>
-      <c r="F14" s="155"/>
-      <c r="G14" s="168"/>
-      <c r="H14" s="156"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="158"/>
+      <c r="H14" s="159"/>
       <c r="I14" s="65" t="s">
         <v>32</v>
       </c>
@@ -3038,37 +3030,29 @@
         <v>33</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="163" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="164"/>
-      <c r="H15" s="165"/>
-      <c r="I15" s="66" t="s">
-        <v>88</v>
+      <c r="F15" s="193" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="194"/>
+      <c r="H15" s="195"/>
+      <c r="I15" s="196" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="46"/>
-      <c r="B16" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>85</v>
-      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="15"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
-      <c r="F16" s="163" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="164"/>
-      <c r="H16" s="165"/>
-      <c r="I16" s="66" t="s">
-        <v>83</v>
-      </c>
+      <c r="F16" s="170"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="172"/>
+      <c r="I16" s="66"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="46"/>
@@ -3076,9 +3060,9 @@
       <c r="C17" s="15"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
-      <c r="F17" s="163"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="165"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="172"/>
       <c r="I17" s="66"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -3087,9 +3071,9 @@
       <c r="C18" s="15"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
-      <c r="F18" s="163"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="165"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="171"/>
+      <c r="H18" s="172"/>
       <c r="I18" s="66"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -3115,7 +3099,7 @@
     </row>
     <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="123" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3134,7 +3118,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="129" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="130"/>
@@ -3150,7 +3134,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="130"/>
@@ -3176,7 +3160,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="129" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F25" s="130"/>
       <c r="G25" s="130"/>
@@ -3191,15 +3175,15 @@
       <c r="D26" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="166" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="164"/>
+      <c r="E26" s="173" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="171"/>
       <c r="G26" s="118" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H26" s="118" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3211,10 +3195,10 @@
       <c r="D27" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="166" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="164"/>
+      <c r="E27" s="173" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="171"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
     </row>
@@ -3237,7 +3221,7 @@
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -3265,7 +3249,7 @@
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -3362,10 +3346,12 @@
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="122" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+      <c r="H39" s="68" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="40" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
@@ -3386,7 +3372,7 @@
       </c>
       <c r="C41" s="12"/>
       <c r="E41" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
@@ -3410,7 +3396,7 @@
       </c>
       <c r="C43" s="12"/>
       <c r="E43" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
@@ -3436,7 +3422,7 @@
       <c r="C45" s="55"/>
       <c r="D45" s="55"/>
       <c r="E45" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
@@ -3462,7 +3448,7 @@
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
       <c r="E47" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
@@ -3490,24 +3476,24 @@
     </row>
     <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
-      <c r="B50" s="153" t="s">
+      <c r="B50" s="164" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="154"/>
-      <c r="D50" s="157" t="s">
+      <c r="C50" s="165"/>
+      <c r="D50" s="166" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="158"/>
+      <c r="E50" s="167"/>
       <c r="F50" s="41"/>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
-      <c r="B51" s="155"/>
-      <c r="C51" s="156"/>
-      <c r="D51" s="159"/>
-      <c r="E51" s="160"/>
+      <c r="B51" s="157"/>
+      <c r="C51" s="159"/>
+      <c r="D51" s="168"/>
+      <c r="E51" s="169"/>
       <c r="F51" s="41"/>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
@@ -3708,14 +3694,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="B50:C51"/>
     <mergeCell ref="D50:E51"/>
     <mergeCell ref="B13:B14"/>
@@ -3726,6 +3704,14 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
@@ -3759,62 +3745,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="174"/>
+      <c r="P2" s="174"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="190" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
-      <c r="L3" s="190"/>
-      <c r="M3" s="190"/>
-      <c r="N3" s="190"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="190"/>
+      <c r="A3" s="174" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="174"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="191"/>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
-      <c r="L4" s="191"/>
-      <c r="M4" s="191"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="191"/>
-      <c r="P4" s="191"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="175"/>
+      <c r="L4" s="175"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="175"/>
     </row>
     <row r="5" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39"/>
@@ -3822,14 +3808,14 @@
         <v>1</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" s="39"/>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="H5" s="39"/>
       <c r="I5" s="119" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J5" s="119"/>
       <c r="K5" s="39"/>
@@ -3858,16 +3844,16 @@
       <c r="P6" s="39"/>
     </row>
     <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="178" t="s">
+      <c r="A7" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="180" t="s">
+      <c r="B7" s="183" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="180" t="s">
+      <c r="D7" s="183" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="70" t="s">
@@ -3876,60 +3862,60 @@
       <c r="F7" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="192" t="s">
+      <c r="G7" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="192"/>
-      <c r="I7" s="182" t="s">
+      <c r="H7" s="176"/>
+      <c r="I7" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="182" t="s">
+      <c r="J7" s="185" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="185" t="s">
+      <c r="L7" s="188" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="185" t="s">
+      <c r="M7" s="188" t="s">
         <v>13</v>
       </c>
       <c r="N7" s="70"/>
       <c r="O7" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="188" t="s">
+      <c r="P7" s="191" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="179"/>
-      <c r="B8" s="181"/>
+      <c r="A8" s="182"/>
+      <c r="B8" s="184"/>
       <c r="C8" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="181"/>
+      <c r="D8" s="184"/>
       <c r="E8" s="71" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="193" t="s">
+      <c r="G8" s="177" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="194"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="184"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="186"/>
+      <c r="J8" s="187"/>
       <c r="K8" s="114"/>
-      <c r="L8" s="186"/>
-      <c r="M8" s="187"/>
+      <c r="L8" s="189"/>
+      <c r="M8" s="190"/>
       <c r="N8" s="71"/>
       <c r="O8" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="189"/>
+      <c r="P8" s="192"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A9" s="72">
@@ -3985,9 +3971,9 @@
       <c r="A10" s="76">
         <v>2</v>
       </c>
-      <c r="B10" s="77" t="str">
+      <c r="B10" s="77">
         <f>'Permohonan Perjadin'!C16</f>
-        <v>Hamdan Mubarok</v>
+        <v>0</v>
       </c>
       <c r="C10" s="121" t="s">
         <v>21</v>
@@ -4309,12 +4295,12 @@
       <c r="K23" s="39"/>
       <c r="L23" s="39"/>
       <c r="M23" s="39"/>
-      <c r="N23" s="176" t="str">
+      <c r="N23" s="179" t="str">
         <f>'Permohonan Perjadin'!H35</f>
         <v>Dr. Ir. I Ketut Kariyasa, M.Si</v>
       </c>
-      <c r="O23" s="176"/>
-      <c r="P23" s="176"/>
+      <c r="O23" s="179"/>
+      <c r="P23" s="179"/>
       <c r="R23" s="107"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -4334,12 +4320,12 @@
       <c r="K24" s="39"/>
       <c r="L24" s="39"/>
       <c r="M24" s="39"/>
-      <c r="N24" s="177" t="str">
+      <c r="N24" s="180" t="str">
         <f>'Permohonan Perjadin'!H36</f>
         <v>NIP. 196904191998031002</v>
       </c>
-      <c r="O24" s="177"/>
-      <c r="P24" s="177"/>
+      <c r="O24" s="180"/>
+      <c r="P24" s="180"/>
       <c r="R24" s="107"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -4362,11 +4348,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="A7:A8"/>
@@ -4377,6 +4358,11 @@
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.55118110236220474" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
